--- a/data/trans_dic/P37A$vacunapreferencia-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunapreferencia-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,7</t>
+          <t>0,86; 2,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,39</t>
+          <t>3,13; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,52</t>
+          <t>1,18; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,28</t>
+          <t>6,21; 10,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,53</t>
+          <t>0,25; 1,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,12</t>
+          <t>1,02; 3,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,04</t>
+          <t>0,43; 2,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,0</t>
+          <t>6,47; 9,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,75</t>
+          <t>0,63; 1,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,33</t>
+          <t>2,32; 4,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,4</t>
+          <t>1,06; 2,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,02</t>
+          <t>6,83; 9,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,79</t>
+          <t>2,27; 4,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,84</t>
+          <t>1,82; 3,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,87</t>
+          <t>0,51; 1,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,52</t>
+          <t>5,09; 8,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,22</t>
+          <t>1,88; 4,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,1</t>
+          <t>1,32; 3,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,55</t>
+          <t>1,52; 3,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,72</t>
+          <t>6,14; 8,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,16</t>
+          <t>2,27; 3,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,22</t>
+          <t>1,77; 3,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,45</t>
+          <t>1,21; 2,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,49</t>
+          <t>6,1; 8,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,35</t>
+          <t>1,74; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,83</t>
+          <t>1,99; 4,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,86</t>
+          <t>0,41; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,68</t>
+          <t>7,36; 11,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,71</t>
+          <t>2,65; 5,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,49</t>
+          <t>1,21; 3,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,65</t>
+          <t>0,82; 2,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 10,06</t>
+          <t>7,21; 10,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,52</t>
+          <t>2,52; 4,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,59</t>
+          <t>1,92; 3,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,0</t>
+          <t>0,83; 2,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,01</t>
+          <t>7,78; 10,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,28</t>
+          <t>2,02; 4,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,22</t>
+          <t>1,37; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,34</t>
+          <t>1,52; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,9</t>
+          <t>5,9; 9,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,93</t>
+          <t>1,62; 3,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,47</t>
+          <t>0,97; 2,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,04</t>
+          <t>1,1; 2,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,42</t>
+          <t>6,15; 8,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,53</t>
+          <t>2,15; 3,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,54</t>
+          <t>1,31; 2,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,79</t>
+          <t>1,49; 2,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,29</t>
+          <t>6,55; 8,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,45</t>
+          <t>2,24; 3,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,69</t>
+          <t>2,45; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,15</t>
+          <t>1,22; 2,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,33</t>
+          <t>6,96; 8,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,2</t>
+          <t>2,06; 3,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,49</t>
+          <t>1,49; 2,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,33</t>
+          <t>1,38; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,0</t>
+          <t>7,14; 8,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,09</t>
+          <t>2,29; 3,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,85</t>
+          <t>2,1; 2,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,42; 2,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,96</t>
+          <t>7,29; 8,48</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51296</t>
+          <t>56852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52931</t>
+          <t>57778</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>114630</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5952; 18737</t>
+          <t>5988; 18950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21156; 44971</t>
+          <t>22019; 45099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8653; 23752</t>
+          <t>7940; 23647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38893; 65301</t>
+          <t>42880; 71245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1798; 10527</t>
+          <t>1690; 10211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7105; 21768</t>
+          <t>7131; 21315</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2899; 13743</t>
+          <t>2914; 14445</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40107; 65271</t>
+          <t>47482; 71066</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8900; 24133</t>
+          <t>8741; 24481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32453; 60712</t>
+          <t>32432; 60072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13943; 32331</t>
+          <t>14304; 33617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85425; 122721</t>
+          <t>97327; 136032</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64408</t>
+          <t>70607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68947</t>
+          <t>78460</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>133355</t>
+          <t>149068</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21909; 46088</t>
+          <t>21820; 45613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18486; 39092</t>
+          <t>18551; 40466</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4983; 19112</t>
+          <t>5206; 19665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31953; 89726</t>
+          <t>53376; 87566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19099; 40818</t>
+          <t>18243; 41285</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13221; 32003</t>
+          <t>13612; 33098</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14794; 37068</t>
+          <t>15896; 37270</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57207; 83630</t>
+          <t>65756; 95861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45973; 80322</t>
+          <t>43900; 75373</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37092; 66092</t>
+          <t>36258; 65380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24696; 50505</t>
+          <t>24978; 49933</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92026; 161100</t>
+          <t>129400; 172404</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>75348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67171</t>
+          <t>72940</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>132992</t>
+          <t>148288</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11029; 29529</t>
+          <t>11794; 30175</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16245; 36616</t>
+          <t>15055; 35975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3107; 14107</t>
+          <t>3086; 14315</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50946; 82283</t>
+          <t>59073; 94986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17374; 39078</t>
+          <t>18109; 38694</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9847; 27121</t>
+          <t>9425; 26796</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6406; 20771</t>
+          <t>6458; 21393</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32436; 93852</t>
+          <t>58532; 88970</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34574; 61645</t>
+          <t>34329; 62861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28887; 55100</t>
+          <t>29456; 55250</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12464; 30829</t>
+          <t>12834; 31592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87714; 163976</t>
+          <t>125713; 171763</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>74470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>76044</t>
+          <t>84367</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>146372</t>
+          <t>158838</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19119; 40299</t>
+          <t>19025; 39879</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12543; 30530</t>
+          <t>12988; 31094</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14108; 31289</t>
+          <t>14241; 32234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58075; 91743</t>
+          <t>58429; 89816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17040; 40779</t>
+          <t>16871; 37644</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9656; 25995</t>
+          <t>10246; 26479</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12166; 31767</t>
+          <t>11529; 31090</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60223; 92170</t>
+          <t>68857; 99113</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41511; 69965</t>
+          <t>42577; 72410</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26207; 50852</t>
+          <t>26205; 50256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29133; 55260</t>
+          <t>29454; 56824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>122341; 167699</t>
+          <t>138193; 182034</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>277278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>516946</t>
+          <t>570824</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74819; 113119</t>
+          <t>73364; 111372</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86116; 126484</t>
+          <t>83812; 125526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42595; 73043</t>
+          <t>41274; 70793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199770; 288312</t>
+          <t>245821; 310395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>67545; 108075</t>
+          <t>69680; 105793</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53628; 88684</t>
+          <t>52958; 85022</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49125; 82588</t>
+          <t>48741; 82379</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>211722; 296987</t>
+          <t>266758; 325441</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>151285; 205842</t>
+          <t>152147; 207189</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147335; 199000</t>
+          <t>146471; 200010</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98108; 143223</t>
+          <t>98580; 142538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>448678; 571131</t>
+          <t>530256; 616274</t>
         </is>
       </c>
     </row>
